--- a/FST16_Wheel_Bearing_Calculator.xlsx
+++ b/FST16_Wheel_Bearing_Calculator.xlsx
@@ -636,11 +636,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -819,7 +819,7 @@
         <v>155</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="R4" s="5" t="n">
         <v>1</v>
@@ -833,12 +833,12 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Schaeffler 61816-2RSR</t>
+          <t>INA 71816-TN</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Thin DGBB (Rubber Sealed)</t>
+          <t>Thin ACBB (40-deg Polyamide)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
@@ -854,56 +854,56 @@
         <v>90</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>13.8</v>
+        <v>16.5</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>13.8</v>
+        <v>19.1</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>3100</v>
+        <v>8000</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>3100</v>
+        <v>10000</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>7.353</v>
+        <v>180</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>Rejected Seal Drag</t>
+          <t>Target Upgrade</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>FAG B71816-C-TPA-P4S-UL</t>
+          <t>Schaeffler 61816-2RSR</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Thin ACBB (15-deg Spindle)</t>
+          <t>Thin DGBB (Rubber Sealed)</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -919,56 +919,56 @@
         <v>90</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>14.6</v>
+        <v>13.8</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>16.6</v>
+        <v>13.8</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>6.747</v>
+        <v>6</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>12000</v>
+        <v>3100</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>19000</v>
+        <v>3100</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>75</v>
+        <v>7.353</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>370</v>
+        <v>50</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>Candidate 15-deg</t>
+          <t>Rejected Seal Drag</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>FAG B71816-E-TPA-P4S-UL</t>
+          <t>FAG B71816-C-TPA-P4S-UL</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Thin ACBB (25-deg Light)</t>
+          <t>Thin ACBB (15-deg Spindle)</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
@@ -984,56 +984,56 @@
         <v>90</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>15.6</v>
+        <v>16.6</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>7.144</v>
+        <v>6.747</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>35</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>9500</v>
+        <v>12000</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>15000</v>
+        <v>19000</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>121.4</v>
+        <v>75</v>
       </c>
       <c r="P7" s="8" t="n">
         <v>145</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="R7" s="5" t="n">
         <v>18</v>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>Target Upgrade</t>
+          <t>Candidate 15-deg</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>FAG B71816-E-TPA-P4S-UM</t>
+          <t>FAG B71816-E-TPA-P4S-UL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Thin ACBB (25-deg Medium)</t>
+          <t>Thin ACBB (25-deg Light)</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -1064,41 +1064,41 @@
         <v>35</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>195.3</v>
+        <v>121.4</v>
       </c>
       <c r="P8" s="8" t="n">
         <v>145</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="R8" s="5" t="n">
         <v>18</v>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>Candidate Medium</t>
+          <t>Target Upgrade</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>FAG B71816-E-TPA-P4S-UH</t>
+          <t>FAG B71816-E-TPA-P4S-UM</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Thin ACBB (25-deg Heavy)</t>
+          <t>Thin ACBB (25-deg Medium)</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -1129,41 +1129,41 @@
         <v>35</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>8200</v>
+        <v>9000</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>590</v>
+        <v>520</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>275.3</v>
+        <v>195.3</v>
       </c>
       <c r="P9" s="8" t="n">
         <v>145</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>Candidate Heavy</t>
+          <t>Candidate Medium</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>FAG HCB71816-E-TPA-P4S-UL</t>
+          <t>FAG B71816-E-TPA-P4S-UH</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Hybrid Ceramic ACBB (Si3N4)</t>
+          <t>Thin ACBB (25-deg Heavy)</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -1179,10 +1179,10 @@
         <v>90</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>9.5</v>
+        <v>13.7</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>10.8</v>
+        <v>15.6</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>25</v>
@@ -1194,41 +1194,41 @@
         <v>35</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>12000</v>
+        <v>8200</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>490</v>
+        <v>590</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>135</v>
+        <v>275.3</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>620</v>
+        <v>440</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>Hybrid Ceramic</t>
+          <t>Candidate Heavy</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>FAG XCB71816-E-TPA-P4S-UL</t>
+          <t>FAG HCB71816-E-TPA-P4S-UL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Cronidur 30 ACBB (F1 Grade)</t>
+          <t>Hybrid Ceramic ACBB (Si3N4)</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
@@ -1244,10 +1244,10 @@
         <v>90</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>25</v>
@@ -1259,106 +1259,106 @@
         <v>35</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>550</v>
+        <v>490</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="P11" s="8" t="n">
         <v>125</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>1250</v>
+        <v>620</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>Cronidur 30 F1</t>
+          <t>Hybrid Ceramic</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Schaeffler 61815-Y</t>
+          <t>FAG XCB71816-E-TPA-P4S-UL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Thin DGBB (FST15 Inner)</t>
+          <t>Cronidur 30 ACBB (F1 Grade)</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>10</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>13.7</v>
+        <v>12.5</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>13.4</v>
+        <v>12</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>6</v>
+        <v>7.144</v>
       </c>
       <c r="K12" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>14000</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>22000</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R12" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="L12" s="7" t="n">
-        <v>8500</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>13000</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>480</v>
-      </c>
-      <c r="O12" s="6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>FST15 Baseline</t>
+          <t>Cronidur 30 F1</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>FAG B71815-E-TPA-P4S-UL</t>
+          <t>Schaeffler 61815-Y</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Thin ACBB (FST15 Stepped)</t>
+          <t>Thin DGBB (FST15 Inner)</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -1374,121 +1374,121 @@
         <v>85</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>14.8</v>
+        <v>13.4</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>7.144</v>
+        <v>6</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>10000</v>
+        <v>8500</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>16000</v>
+        <v>13000</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>115</v>
+        <v>7.1</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>360</v>
+        <v>42</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>FST15 Stepped ACBB</t>
+          <t>FST15 Baseline</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Schaeffler 61916</t>
+          <t>FAG B71815-E-TPA-P4S-UL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Medium Thin DGBB (ISO 19)</t>
+          <t>Thin ACBB (FST15 Stepped)</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>26.5</v>
+        <v>13.2</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>24</v>
+        <v>14.8</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>10</v>
+        <v>7.144</v>
       </c>
       <c r="K14" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>16000</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>360</v>
+      </c>
+      <c r="R14" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="L14" s="7" t="n">
-        <v>6700</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>620</v>
-      </c>
-      <c r="O14" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="P14" s="8" t="n">
-        <v>380</v>
-      </c>
-      <c r="Q14" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>Rejected Packaging</t>
+          <t>FST15 Stepped ACBB</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>FAG B71916-E-TPA-P4S-UL</t>
+          <t>Schaeffler 61916</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Angular Contact (ISO 19)</t>
+          <t>Medium Thin DGBB (ISO 19)</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -1504,40 +1504,40 @@
         <v>95</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>33.5</v>
+        <v>26.5</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>24</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>10</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>8500</v>
+        <v>6700</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>13000</v>
+        <v>8000</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>680</v>
+        <v>620</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>185</v>
+        <v>12</v>
       </c>
       <c r="P15" s="8" t="n">
         <v>380</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>450</v>
+        <v>75</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
@@ -1548,126 +1548,126 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Schaeffler 6016</t>
+          <t>FAG B71916-E-TPA-P4S-UL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Standard DGBB (ISO 02)</t>
+          <t>Angular Contact (ISO 19)</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>80</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>102.5</v>
+        <v>95</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>51</v>
+        <v>33.5</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>5600</v>
+        <v>8500</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>6700</v>
+        <v>13000</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>780</v>
+        <v>680</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>850</v>
+        <v>380</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>Rejected Mass</t>
+          <t>Rejected Packaging</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>FAG 7216-B-XL-TVP</t>
+          <t>Schaeffler 6016</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Standard ACBB (ISO 02)</t>
+          <t>Standard DGBB (ISO 02)</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>80</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>110</v>
+        <v>102.5</v>
       </c>
       <c r="G17" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>5600</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>6700</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>780</v>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>850</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="H17" s="6" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>4800</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>6300</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>1100</v>
-      </c>
-      <c r="O17" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>1450</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>140</v>
-      </c>
       <c r="R17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
@@ -1678,142 +1678,142 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>FAG 32016-X-XL</t>
+          <t>FAG 7216-B-XL-TVP</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Tapered Roller Bearing</t>
+          <t>Standard ACBB (ISO 02)</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>80</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>102.5</v>
+        <v>110</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>212</v>
+        <v>76.5</v>
       </c>
       <c r="I18" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>24</v>
-      </c>
       <c r="L18" s="7" t="n">
-        <v>3000</v>
+        <v>4800</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>4300</v>
+        <v>6300</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>2200</v>
+        <v>1100</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>850</v>
+        <v>320</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>1250</v>
+        <v>1450</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="R18" s="5" t="n">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>Rejected Mass Friction</t>
+          <t>Rejected Mass</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>FAG 3216-B-TVH</t>
+          <t>FAG 32016-X-XL</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Double Row Angular Contact</t>
+          <t>Tapered Roller Bearing</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>80</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>44.4</v>
+        <v>29</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>110</v>
+        <v>102.5</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>24</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>3800</v>
+        <v>4300</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1400</v>
+        <v>2200</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>420</v>
+        <v>850</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>2450</v>
+        <v>1250</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>Rejected Road Car Unit</t>
+          <t>Rejected Mass Friction</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>FAG QJ216-XL-MPA</t>
+          <t>FAG 3216-B-TVH</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Four-Point Contact Ball</t>
+          <t>Double Row Angular Contact</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -1823,48 +1823,113 @@
         <v>140</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>26</v>
+        <v>44.4</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>110</v>
       </c>
       <c r="G20" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>2800</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>3800</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>420</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>2450</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>Rejected Road Car Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>FAG QJ216-XL-MPA</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Four-Point Contact Ball</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="G21" s="6" t="n">
         <v>136</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H21" s="6" t="n">
         <v>137</v>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="I21" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="J21" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="K21" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L21" s="7" t="n">
         <v>3400</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M21" s="7" t="n">
         <v>5300</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N21" s="6" t="n">
         <v>1300</v>
       </c>
-      <c r="O20" s="6" t="n">
+      <c r="O21" s="6" t="n">
         <v>350</v>
       </c>
-      <c r="P20" s="8" t="n">
+      <c r="P21" s="8" t="n">
         <v>1700</v>
       </c>
-      <c r="Q20" s="8" t="n">
+      <c r="Q21" s="8" t="n">
         <v>260</v>
       </c>
-      <c r="R20" s="5" t="n">
+      <c r="R21" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="S21" s="3" t="inlineStr">
         <is>
           <t>Rejected Split Ring</t>
         </is>
@@ -1952,11 +2017,11 @@
         </is>
       </c>
       <c r="D6" s="14">
-        <f>VLOOKUP(C6, Bearing_Database!A4:S20, 2, FALSE)</f>
+        <f>VLOOKUP(C6, Bearing_Database!A4:S25, 2, FALSE)</f>
         <v/>
       </c>
       <c r="E6" s="15">
-        <f>"Bore: " &amp; VLOOKUP(C6, Bearing_Database!A4:S20, 3, FALSE) &amp; " mm | Angle: " &amp; VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE) &amp; " deg"</f>
+        <f>"Bore: " &amp; VLOOKUP(C6, Bearing_Database!A4:S25, 3, FALSE) &amp; " mm | Angle: " &amp; VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE) &amp; " deg"</f>
         <v/>
       </c>
     </row>
@@ -1972,11 +2037,11 @@
         </is>
       </c>
       <c r="D7" s="14">
-        <f>VLOOKUP(C7, Bearing_Database!A4:S20, 2, FALSE)</f>
+        <f>VLOOKUP(C7, Bearing_Database!A4:S25, 2, FALSE)</f>
         <v/>
       </c>
       <c r="E7" s="15">
-        <f>"Bore: " &amp; VLOOKUP(C7, Bearing_Database!A4:S20, 3, FALSE) &amp; " mm | Angle: " &amp; VLOOKUP(C7, Bearing_Database!A4:S20, 9, FALSE) &amp; " deg"</f>
+        <f>"Bore: " &amp; VLOOKUP(C7, Bearing_Database!A4:S25, 3, FALSE) &amp; " mm | Angle: " &amp; VLOOKUP(C7, Bearing_Database!A4:S25, 9, FALSE) &amp; " deg"</f>
         <v/>
       </c>
     </row>
@@ -2214,7 +2279,7 @@
         </is>
       </c>
       <c r="C22" s="6">
-        <f>IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, (VLOOKUP(C6, Bearing_Database!A4:S20, 6, FALSE)/2)*TAN(RADIANS(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE))), 0)</f>
+        <f>IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, (VLOOKUP(C6, Bearing_Database!A4:S25, 6, FALSE)/2)*TAN(RADIANS(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE))), 0)</f>
         <v/>
       </c>
       <c r="D22" s="17" t="inlineStr">
@@ -2235,7 +2300,7 @@
         </is>
       </c>
       <c r="C23" s="6">
-        <f>IF(VLOOKUP(C7, Bearing_Database!A4:S20, 9, FALSE)&gt;0, (VLOOKUP(C7, Bearing_Database!A4:S20, 6, FALSE)/2)*TAN(RADIANS(VLOOKUP(C7, Bearing_Database!A4:S20, 9, FALSE))), 0)</f>
+        <f>IF(VLOOKUP(C7, Bearing_Database!A4:S25, 9, FALSE)&gt;0, (VLOOKUP(C7, Bearing_Database!A4:S25, 6, FALSE)/2)*TAN(RADIANS(VLOOKUP(C7, Bearing_Database!A4:S25, 9, FALSE))), 0)</f>
         <v/>
       </c>
       <c r="D23" s="17" t="inlineStr">
@@ -2399,11 +2464,11 @@
         </is>
       </c>
       <c r="C32" s="23">
-        <f>IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, MAX(C26, 0.5*C26+0.38*C28), MAX(C26, 0.6*C26+0.5*C28))</f>
+        <f>IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, MAX(C26, 0.5*C26+0.38*C28), MAX(C26, 0.6*C26+0.5*C28))</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>IF(VLOOKUP(C7, Bearing_Database!A4:S20, 9, FALSE)&gt;0, MAX(C27, 0.5*C27+0.38*C28), MAX(C27, 0.6*C27+0.5*C28))</f>
+        <f>IF(VLOOKUP(C7, Bearing_Database!A4:S25, 9, FALSE)&gt;0, MAX(C27, 0.5*C27+0.38*C28), MAX(C27, 0.6*C27+0.5*C28))</f>
         <v/>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -2424,11 +2489,11 @@
         </is>
       </c>
       <c r="C33" s="21">
-        <f>(VLOOKUP(C6, Bearing_Database!A4:S20, 8, FALSE)*1000)/C32</f>
+        <f>(VLOOKUP(C6, Bearing_Database!A4:S25, 8, FALSE)*1000)/C32</f>
         <v/>
       </c>
       <c r="D33" s="21">
-        <f>(VLOOKUP(C7, Bearing_Database!A4:S20, 8, FALSE)*1000)/D32</f>
+        <f>(VLOOKUP(C7, Bearing_Database!A4:S25, 8, FALSE)*1000)/D32</f>
         <v/>
       </c>
       <c r="E33" s="17" t="inlineStr">
@@ -2499,11 +2564,11 @@
         </is>
       </c>
       <c r="C36" s="24">
-        <f>(10^6/(60*C34)) * ((VLOOKUP(C6, Bearing_Database!A4:S20, 7, FALSE)*1000)/C35)^3</f>
+        <f>(10^6/(60*C34)) * ((VLOOKUP(C6, Bearing_Database!A4:S25, 7, FALSE)*1000)/C35)^3</f>
         <v/>
       </c>
       <c r="D36" s="24">
-        <f>(10^6/(60*C34)) * ((VLOOKUP(C7, Bearing_Database!A4:S20, 7, FALSE)*1000)/D35)^3</f>
+        <f>(10^6/(60*C34)) * ((VLOOKUP(C7, Bearing_Database!A4:S25, 7, FALSE)*1000)/D35)^3</f>
         <v/>
       </c>
       <c r="E36" s="17" t="inlineStr">
@@ -2582,7 +2647,7 @@
         </is>
       </c>
       <c r="C41" s="24">
-        <f>0.5 * (VLOOKUP(C6, Bearing_Database!A4:S20, 14, FALSE)*1000000) * ((C24/1000)^2) * (PI()/180)</f>
+        <f>0.5 * (VLOOKUP(C6, Bearing_Database!A4:S25, 14, FALSE)*1000000) * ((C24/1000)^2) * (PI()/180)</f>
         <v/>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -2699,7 +2764,7 @@
         </is>
       </c>
       <c r="C48" s="23">
-        <f>IF(ISNUMBER(SEARCH("-UH", C6)), 712, IF(ISNUMBER(SEARCH("-UM", C6)), 302, IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, 84, (VLOOKUP(C6, Bearing_Database!A4:S20, 15, FALSE)*1000)*0.100)))</f>
+        <f>IF(ISNUMBER(SEARCH("-UH", C6)), 712, IF(ISNUMBER(SEARCH("-UM", C6)), 302, IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, 84, (VLOOKUP(C6, Bearing_Database!A4:S25, 15, FALSE)*1000)*0.100)))</f>
         <v/>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -2985,7 +3050,7 @@
         </is>
       </c>
       <c r="C65" s="31">
-        <f>C34 * VLOOKUP(C6, Bearing_Database!A4:S20, 6, FALSE)</f>
+        <f>C34 * VLOOKUP(C6, Bearing_Database!A4:S25, 6, FALSE)</f>
         <v/>
       </c>
       <c r="D65" s="17" t="inlineStr">
@@ -3006,7 +3071,7 @@
         </is>
       </c>
       <c r="C66" s="8">
-        <f>(C34/2) * (1 - (VLOOKUP(C6, Bearing_Database!A4:S20, 10, FALSE)/VLOOKUP(C6, Bearing_Database!A4:S20, 6, FALSE))*COS(RADIANS(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE))))</f>
+        <f>(C34/2) * (1 - (VLOOKUP(C6, Bearing_Database!A4:S25, 10, FALSE)/VLOOKUP(C6, Bearing_Database!A4:S25, 6, FALSE))*COS(RADIANS(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE))))</f>
         <v/>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -3027,7 +3092,7 @@
         </is>
       </c>
       <c r="C67" s="8">
-        <f>(C34/2) * (VLOOKUP(C6, Bearing_Database!A4:S20, 6, FALSE)/VLOOKUP(C6, Bearing_Database!A4:S20, 10, FALSE)) * (1 - ((VLOOKUP(C6, Bearing_Database!A4:S20, 10, FALSE)/VLOOKUP(C6, Bearing_Database!A4:S20, 6, FALSE))*COS(RADIANS(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE))))^2)</f>
+        <f>(C34/2) * (VLOOKUP(C6, Bearing_Database!A4:S25, 6, FALSE)/VLOOKUP(C6, Bearing_Database!A4:S25, 10, FALSE)) * (1 - ((VLOOKUP(C6, Bearing_Database!A4:S25, 10, FALSE)/VLOOKUP(C6, Bearing_Database!A4:S25, 6, FALSE))*COS(RADIANS(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE))))^2)</f>
         <v/>
       </c>
       <c r="D67" s="17" t="inlineStr">
@@ -3048,7 +3113,7 @@
         </is>
       </c>
       <c r="C68" s="27">
-        <f>((4/3)*PI()*((VLOOKUP(C6, Bearing_Database!A4:S20, 10, FALSE)/2000)^3)*7800) * (VLOOKUP(C6, Bearing_Database!A4:S20, 6, FALSE)/2000) * ((2*PI()*C66/60)^2)</f>
+        <f>((4/3)*PI()*((VLOOKUP(C6, Bearing_Database!A4:S25, 10, FALSE)/2000)^3)*7800) * (VLOOKUP(C6, Bearing_Database!A4:S25, 6, FALSE)/2000) * ((2*PI()*C66/60)^2)</f>
         <v/>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -3069,7 +3134,7 @@
         </is>
       </c>
       <c r="C69" s="32">
-        <f>(0.1 * ((4/3)*PI()*((VLOOKUP(C6, Bearing_Database!A4:S20, 10, FALSE)/2000)^3)*7800) * ((VLOOKUP(C6, Bearing_Database!A4:S20, 10, FALSE)/1000)^2)) * (2*PI()*C67/60) * (2*PI()*C66/60) * SIN(RADIANS(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE))) * 1000</f>
+        <f>(0.1 * ((4/3)*PI()*((VLOOKUP(C6, Bearing_Database!A4:S25, 10, FALSE)/2000)^3)*7800) * ((VLOOKUP(C6, Bearing_Database!A4:S25, 10, FALSE)/1000)^2)) * (2*PI()*C67/60) * (2*PI()*C66/60) * SIN(RADIANS(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE))) * 1000</f>
         <v/>
       </c>
       <c r="D69" s="17" t="inlineStr">
@@ -3090,7 +3155,7 @@
         </is>
       </c>
       <c r="C70" s="23">
-        <f>IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, VLOOKUP(C6, Bearing_Database!A4:S20, 11, FALSE) * ((C69/1000) / ((VLOOKUP(C6, Bearing_Database!A4:S20, 10, FALSE)/2000) * 0.06)) * SIN(RADIANS(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE))), 0.01 * (VLOOKUP(C6, Bearing_Database!A4:S20, 8, FALSE)*1000))</f>
+        <f>IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, VLOOKUP(C6, Bearing_Database!A4:S25, 11, FALSE) * ((C69/1000) / ((VLOOKUP(C6, Bearing_Database!A4:S25, 10, FALSE)/2000) * 0.06)) * SIN(RADIANS(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE))), 0.01 * (VLOOKUP(C6, Bearing_Database!A4:S25, 8, FALSE)*1000))</f>
         <v/>
       </c>
       <c r="D70" s="17" t="inlineStr">
@@ -3165,7 +3230,7 @@
         </is>
       </c>
       <c r="C75" s="5">
-        <f>45000 * (C34^(-0.83)) * ((VLOOKUP(C6, Bearing_Database!A4:S20, 6, FALSE))^(-0.5))</f>
+        <f>45000 * (C34^(-0.83)) * ((VLOOKUP(C6, Bearing_Database!A4:S25, 6, FALSE))^(-0.5))</f>
         <v/>
       </c>
       <c r="D75" s="17" t="inlineStr">
@@ -3266,7 +3331,7 @@
         <v/>
       </c>
       <c r="F80" s="20">
-        <f>(VLOOKUP(C6, Bearing_Database!A4:S20, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, MAX(E80, 0.5*E80+0.38*ABS(C80)), MAX(E80, 0.6*E80+0.5*ABS(C80))))</f>
+        <f>(VLOOKUP(C6, Bearing_Database!A4:S25, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, MAX(E80, 0.5*E80+0.38*ABS(C80)), MAX(E80, 0.6*E80+0.5*ABS(C80))))</f>
         <v/>
       </c>
       <c r="G80" s="22">
@@ -3292,7 +3357,7 @@
         <v/>
       </c>
       <c r="F81" s="20">
-        <f>(VLOOKUP(C6, Bearing_Database!A4:S20, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, MAX(E81, 0.5*E81+0.38*ABS(C81)), MAX(E81, 0.6*E81+0.5*ABS(C81))))</f>
+        <f>(VLOOKUP(C6, Bearing_Database!A4:S25, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, MAX(E81, 0.5*E81+0.38*ABS(C81)), MAX(E81, 0.6*E81+0.5*ABS(C81))))</f>
         <v/>
       </c>
       <c r="G81" s="22">
@@ -3318,7 +3383,7 @@
         <v/>
       </c>
       <c r="F82" s="20">
-        <f>(VLOOKUP(C6, Bearing_Database!A4:S20, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, MAX(E82, 0.5*E82+0.38*ABS(C82)), MAX(E82, 0.6*E82+0.5*ABS(C82))))</f>
+        <f>(VLOOKUP(C6, Bearing_Database!A4:S25, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, MAX(E82, 0.5*E82+0.38*ABS(C82)), MAX(E82, 0.6*E82+0.5*ABS(C82))))</f>
         <v/>
       </c>
       <c r="G82" s="22">
@@ -3344,7 +3409,7 @@
         <v/>
       </c>
       <c r="F83" s="20">
-        <f>(VLOOKUP(C6, Bearing_Database!A4:S20, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, MAX(E83, 0.5*E83+0.38*ABS(C83)), MAX(E83, 0.6*E83+0.5*ABS(C83))))</f>
+        <f>(VLOOKUP(C6, Bearing_Database!A4:S25, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, MAX(E83, 0.5*E83+0.38*ABS(C83)), MAX(E83, 0.6*E83+0.5*ABS(C83))))</f>
         <v/>
       </c>
       <c r="G83" s="22">
@@ -3370,7 +3435,7 @@
         <v/>
       </c>
       <c r="F84" s="20">
-        <f>(VLOOKUP(C6, Bearing_Database!A4:S20, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, MAX(E84, 0.5*E84+0.38*ABS(C84)), MAX(E84, 0.6*E84+0.5*ABS(C84))))</f>
+        <f>(VLOOKUP(C6, Bearing_Database!A4:S25, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, MAX(E84, 0.5*E84+0.38*ABS(C84)), MAX(E84, 0.6*E84+0.5*ABS(C84))))</f>
         <v/>
       </c>
       <c r="G84" s="22">
@@ -3396,7 +3461,7 @@
         <v/>
       </c>
       <c r="F85" s="20">
-        <f>(VLOOKUP(C6, Bearing_Database!A4:S20, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, MAX(E85, 0.5*E85+0.38*ABS(C85)), MAX(E85, 0.6*E85+0.5*ABS(C85))))</f>
+        <f>(VLOOKUP(C6, Bearing_Database!A4:S25, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, MAX(E85, 0.5*E85+0.38*ABS(C85)), MAX(E85, 0.6*E85+0.5*ABS(C85))))</f>
         <v/>
       </c>
       <c r="G85" s="22">
@@ -3422,7 +3487,7 @@
         <v/>
       </c>
       <c r="F86" s="20">
-        <f>(VLOOKUP(C6, Bearing_Database!A4:S20, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, MAX(E86, 0.5*E86+0.38*ABS(C86)), MAX(E86, 0.6*E86+0.5*ABS(C86))))</f>
+        <f>(VLOOKUP(C6, Bearing_Database!A4:S25, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, MAX(E86, 0.5*E86+0.38*ABS(C86)), MAX(E86, 0.6*E86+0.5*ABS(C86))))</f>
         <v/>
       </c>
       <c r="G86" s="22">
@@ -3448,7 +3513,7 @@
         <v/>
       </c>
       <c r="F87" s="20">
-        <f>(VLOOKUP(C6, Bearing_Database!A4:S20, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S20, 9, FALSE)&gt;0, MAX(E87, 0.5*E87+0.38*ABS(C87)), MAX(E87, 0.6*E87+0.5*ABS(C87))))</f>
+        <f>(VLOOKUP(C6, Bearing_Database!A4:S25, 8, FALSE)*1000)/(IF(VLOOKUP(C6, Bearing_Database!A4:S25, 9, FALSE)&gt;0, MAX(E87, 0.5*E87+0.38*ABS(C87)), MAX(E87, 0.6*E87+0.5*ABS(C87))))</f>
         <v/>
       </c>
       <c r="G87" s="22">
